--- a/branches/main/ValueSet-mii-vs-sdd-ausbildung.xlsx
+++ b/branches/main/ValueSet-mii-vs-sdd-ausbildung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:35:38+00:00</t>
+    <t>2026-09-14T21:09:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/ValueSet-mii-vs-sdd-ausbildung.xlsx
+++ b/branches/main/ValueSet-mii-vs-sdd-ausbildung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:09:09+00:00</t>
+    <t>2026-09-14T21:29:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
